--- a/modules/conjoint/docs/Conjoint_Config_Template.xlsx
+++ b/modules/conjoint/docs/Conjoint_Config_Template.xlsx
@@ -9,15 +9,14 @@
     <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Attributes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Custom_Slides" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Custom_Images" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Design" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Instructions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Design" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Instructions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="278">
   <si>
     <t xml:space="preserve">TURAS Conjoint Analysis Configuration</t>
   </si>
@@ -208,18 +207,6 @@
     <t xml:space="preserve">TRUE or FALSE</t>
   </si>
   <si>
-    <t xml:space="preserve">base_level_method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Which level serves as baseline (utility = 0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">first or last</t>
-  </si>
-  <si>
     <t xml:space="preserve">HIERARCHICAL BAYES SETTINGS</t>
   </si>
   <si>
@@ -334,18 +321,93 @@
     <t xml:space="preserve">Automatically detect significant interactions</t>
   </si>
   <si>
+    <t xml:space="preserve">interaction_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum number of interaction terms to include</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integer 1-6</t>
+  </si>
+  <si>
     <t xml:space="preserve">WILLINGNESS TO PAY</t>
   </si>
   <si>
     <t xml:space="preserve">wtp_price_attribute</t>
   </si>
   <si>
-    <t xml:space="preserve">Name of the price attribute (leave blank to skip WTP)</t>
+    <t xml:space="preserve">Name of the price attribute. Leave blank and an attribute named price/cost/fee is used automatically; set wtp_enabled = N to skip WTP entirely</t>
   </si>
   <si>
     <t xml:space="preserve">Attribute name from Attributes sheet</t>
   </si>
   <si>
+    <t xml:space="preserve">wtp_enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculate willingness to pay (Y/N)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y or N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEST-WORST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bw_method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sequential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best-worst estimation approach. Only sequential is implemented; simultaneous refuses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABS EXPORT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generate_tabs_export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write per-respondent attribute importance in the shape the tabs module reads as an Allocation question, so conjoint results can be crosstabbed. Requires estimation_method = hb or latent_class.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tabs_question_code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CJIMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuestionCode for the exported importance question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Letters, digits and underscores, starting with a letter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA QUALITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">min_responses_per_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum observations required per attribute level before a warning is raised</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive integer</t>
+  </si>
+  <si>
     <t xml:space="preserve">wtp_method</t>
   </si>
   <si>
@@ -406,16 +468,10 @@
     <t xml:space="preserve">HTML REPORT</t>
   </si>
   <si>
-    <t xml:space="preserve">generate_html_report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate interactive HTML analysis report</t>
-  </si>
-  <si>
     <t xml:space="preserve">generate_html_simulator</t>
   </si>
   <si>
-    <t xml:space="preserve">Generate standalone HTML market simulator</t>
+    <t xml:space="preserve">Generate the standalone HTML market simulator (a self-contained file the client can open and share)</t>
   </si>
   <si>
     <t xml:space="preserve">brand_colour</t>
@@ -448,7 +504,7 @@
     <t xml:space="preserve">Conjoint Analysis</t>
   </si>
   <si>
-    <t xml:space="preserve">Project name displayed in report header</t>
+    <t xml:space="preserve">Project name. Appears in the report header and in the stats pack Declaration sheet.</t>
   </si>
   <si>
     <t xml:space="preserve">Free text</t>
@@ -466,7 +522,7 @@
     <t xml:space="preserve">The Research LampPost</t>
   </si>
   <si>
-    <t xml:space="preserve">Company name for report header</t>
+    <t xml:space="preserve">Company or white-label partner name. Appears in the report header and as the research house in the stats pack Declaration sheet.</t>
   </si>
   <si>
     <t xml:space="preserve">HTML REPORT INSIGHTS</t>
@@ -526,19 +582,13 @@
     <t xml:space="preserve">Include custom slides in HTML report (see Custom_Slides sheet)</t>
   </si>
   <si>
-    <t xml:space="preserve">include_custom_images</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include custom images in HTML report (see Custom_Images sheet)</t>
-  </si>
-  <si>
     <t xml:space="preserve">ANALYST &amp; ABOUT</t>
   </si>
   <si>
     <t xml:space="preserve">analyst_name</t>
   </si>
   <si>
-    <t xml:space="preserve">Analyst name for About page</t>
+    <t xml:space="preserve">Analyst name. Appears on the report About page and in the stats pack Declaration sheet.</t>
   </si>
   <si>
     <t xml:space="preserve">analyst_email</t>
@@ -592,30 +642,6 @@
     <t xml:space="preserve">Label for the None/no-choice option</t>
   </si>
   <si>
-    <t xml:space="preserve">OPTIMIZER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">optimizer_method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exhaustive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product optimization search method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exhaustive or greedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">optimizer_max_products</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximum products in optimizer scenarios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integer 1-12</t>
-  </si>
-  <si>
     <t xml:space="preserve">ALCHEMER IMPORT</t>
   </si>
   <si>
@@ -670,34 +696,7 @@
     <t xml:space="preserve">generate_stats_pack</t>
   </si>
   <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate a diagnostic stats pack workbook alongside main output. The stats pack provides a full audit trail of data received, methods used, assumptions, and reproducibility — designed for advanced partners and research statisticians. Output file is named {output}_stats_pack.xlsx.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y or N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STUDY IDENTIFICATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project name — appears in the stats pack Declaration sheet for identification and sign-off purposes. Leave blank if not using stats pack.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyst_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyst name — appears in the stats pack Declaration sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research_House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research organisation name — appears in the stats pack Declaration sheet. Use your company or white-label partner name.</t>
+    <t xml:space="preserve">Generate a diagnostic stats pack workbook alongside main output. The stats pack provides a full audit trail of data received, methods used, assumptions, and reproducibility. This is a contractual deliverable. Output file is named {output}_stats_pack.xlsx.</t>
   </si>
   <si>
     <t xml:space="preserve">Conjoint Attribute Definitions</t>
@@ -724,31 +723,31 @@
     <t xml:space="preserve">LevelNames</t>
   </si>
   <si>
-    <t xml:space="preserve">Brand</t>
+    <t xml:space="preserve">EXAMPLE — Brand</t>
   </si>
   <si>
     <t xml:space="preserve">Apple, Samsung, Google, OnePlus</t>
   </si>
   <si>
-    <t xml:space="preserve">Price</t>
+    <t xml:space="preserve">EXAMPLE — Price</t>
   </si>
   <si>
     <t xml:space="preserve">$299, $399, $499, $599</t>
   </si>
   <si>
-    <t xml:space="preserve">Screen Size</t>
+    <t xml:space="preserve">EXAMPLE — Screen Size</t>
   </si>
   <si>
     <t xml:space="preserve">5.5 inch, 6.1 inch, 6.7 inch</t>
   </si>
   <si>
-    <t xml:space="preserve">Battery Life</t>
+    <t xml:space="preserve">EXAMPLE — Battery Life</t>
   </si>
   <si>
     <t xml:space="preserve">12 hours, 18 hours, 24 hours</t>
   </si>
   <si>
-    <t xml:space="preserve">Camera Quality</t>
+    <t xml:space="preserve">EXAMPLE — Camera Quality</t>
   </si>
   <si>
     <t xml:space="preserve">Basic, Good, Excellent</t>
@@ -778,33 +777,6 @@
     <t xml:space="preserve">## Key Findings
 - Brand is the primary driver
 - Price sensitivity is moderate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custom Images for HTML Report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add images to embed in the HTML report. Images are base64-encoded for self-contained output.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Image Path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panel Placement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[REQUIRED] Path to image file (PNG, JPG)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Caption below image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] overview, utilities, diagnostics, about</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Display order (1, 2, 3...)</t>
   </si>
   <si>
     <t xml:space="preserve">Experimental Design Matrix (Optional)</t>
@@ -1671,30 +1643,30 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="11" t="s">
+      <c r="B23" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="C23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="s">
+      <c r="E23" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="s">
@@ -1735,67 +1707,67 @@
         <v>76</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>78</v>
-      </c>
       <c r="E26" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" s="11" t="s">
+      <c r="E27" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E27" s="7" t="s">
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" s="11" t="s">
+      <c r="C29" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E29" s="7" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
@@ -1825,37 +1797,37 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" s="11" t="s">
+      <c r="B33" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E33" s="7" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
@@ -1864,24 +1836,24 @@
         <v>100</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="C35" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" s="11" t="s">
+      <c r="E35" s="7" t="s">
         <v>104</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="36">
@@ -1928,85 +1900,77 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="11" t="s">
+      <c r="B40" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="C40" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="11" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="s">
+      <c r="E40" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>62</v>
-      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>122</v>
-      </c>
       <c r="E42" s="7" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -2015,198 +1979,182 @@
     </row>
     <row r="45">
       <c r="A45" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E45" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>62</v>
-      </c>
+      <c r="A46" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E47" s="7" t="s">
         <v>133</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E48" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B48" s="6" t="s">
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>144</v>
-      </c>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
+      <c r="A52" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>153</v>
-      </c>
+      <c r="A53" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>153</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B56" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D56" s="11" t="s">
+      <c r="E56" s="7" t="s">
         <v>159</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="57">
@@ -2214,47 +2162,55 @@
         <v>160</v>
       </c>
       <c r="B57" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
+      <c r="C58" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E59" s="7" t="s">
         <v>163</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
@@ -2263,50 +2219,58 @@
     </row>
     <row r="61">
       <c r="A61" s="12" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>62</v>
+        <v>172</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>62</v>
+        <v>172</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
+      <c r="A63" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>14</v>
@@ -2315,15 +2279,15 @@
         <v>4</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>14</v>
@@ -2332,95 +2296,79 @@
         <v>4</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>179</v>
-      </c>
+      <c r="A66" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>144</v>
+        <v>184</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D68" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>184</v>
-      </c>
+      <c r="A68" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="9"/>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
+      <c r="A69" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D70" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>62</v>
-      </c>
+      <c r="A70" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>189</v>
+        <v>14</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>4</v>
@@ -2429,84 +2377,92 @@
         <v>190</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="s">
+      <c r="A72" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
+      <c r="B72" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>193</v>
+        <v>14</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="s">
+      <c r="A75" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
+      <c r="B75" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>62</v>
-      </c>
+      <c r="A76" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B76" s="9"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="9"/>
+      <c r="E76" s="9"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>203</v>
+        <v>99</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>4</v>
@@ -2515,135 +2471,135 @@
         <v>204</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>205</v>
+        <v>62</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="C78" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D78" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="C78" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D78" s="11" t="s">
+      <c r="E78" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="E78" s="7" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D79" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>205</v>
-      </c>
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B81" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="C81" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D81" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="C80" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D80" s="11" t="s">
+      <c r="E81" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="E80" s="7" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B82" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="C82" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D82" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="C82" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D82" s="11" t="s">
+      <c r="E82" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="E82" s="7" t="s">
+      <c r="B83" s="6" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="9" t="s">
+      <c r="C83" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D83" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
+      <c r="E83" s="7" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="s">
         <v>221</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>14</v>
+        <v>222</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>144</v>
+        <v>214</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D85" s="11" t="s">
+      <c r="A85" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="E85" s="7" t="s">
-        <v>144</v>
-      </c>
+      <c r="B85" s="9"/>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="s">
         <v>225</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>4</v>
@@ -2652,41 +2608,43 @@
         <v>226</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A32:E32"/>
     <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A41:E41"/>
     <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A75:E75"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A85:E85"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20:B20">
       <formula1>0.8</formula1>
       <formula2>0.99</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B24:B24">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B23:B23">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25:B25">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B24:B24">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -2694,7 +2652,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="19">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="18">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"generic,alchemer"</xm:f>
@@ -2727,87 +2685,81 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"first,last"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B22:B22</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
             <xm:f>"bic,aic"</xm:f>
           </x14:formula1>
-          <xm:sqref>B32:B32</xm:sqref>
+          <xm:sqref>B31:B31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B35:B35</xm:sqref>
+          <xm:sqref>B34:B34</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B38:B38</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"sequential"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B40:B40</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B42:B42</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"marginal,simulation"</xm:f>
           </x14:formula1>
-          <xm:sqref>B38:B38</xm:sqref>
+          <xm:sqref>B47:B47</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B41:B41</xm:sqref>
+          <xm:sqref>B50:B50</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"logit,first_choice,rfc"</xm:f>
           </x14:formula1>
-          <xm:sqref>B42:B42</xm:sqref>
+          <xm:sqref>B51:B51</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B45:B45</xm:sqref>
+          <xm:sqref>B54:B54</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B46:B46</xm:sqref>
+          <xm:sqref>B69:B69</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B61:B61</xm:sqref>
+          <xm:sqref>B77:B77</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B62:B62</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B70:B70</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"exhaustive,greedy"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B73:B73</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B76:B76</xm:sqref>
+          <xm:sqref>B80:B80</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B82:B82</xm:sqref>
+          <xm:sqref>B86:B86</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3018,7 +2970,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
@@ -3095,12 +3047,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="35.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="35.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -3110,185 +3056,6 @@
     <row r="2">
       <c r="A2" s="2" t="s">
         <v>254</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="10">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"overview,utilities,diagnostics,simulator,wtp,about"</xm:f>
-          </x14:formula1>
-          <xm:sqref>C6:C6</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"overview,utilities,diagnostics,simulator,wtp,about"</xm:f>
-          </x14:formula1>
-          <xm:sqref>C7:C7</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"overview,utilities,diagnostics,simulator,wtp,about"</xm:f>
-          </x14:formula1>
-          <xm:sqref>C8:C8</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"overview,utilities,diagnostics,simulator,wtp,about"</xm:f>
-          </x14:formula1>
-          <xm:sqref>C9:C9</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"overview,utilities,diagnostics,simulator,wtp,about"</xm:f>
-          </x14:formula1>
-          <xm:sqref>C10:C10</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"overview,utilities,diagnostics,simulator,wtp,about"</xm:f>
-          </x14:formula1>
-          <xm:sqref>C11:C11</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"overview,utilities,diagnostics,simulator,wtp,about"</xm:f>
-          </x14:formula1>
-          <xm:sqref>C12:C12</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"overview,utilities,diagnostics,simulator,wtp,about"</xm:f>
-          </x14:formula1>
-          <xm:sqref>C13:C13</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"overview,utilities,diagnostics,simulator,wtp,about"</xm:f>
-          </x14:formula1>
-          <xm:sqref>C14:C14</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"overview,utilities,diagnostics,simulator,wtp,about"</xm:f>
-          </x14:formula1>
-          <xm:sqref>C15:C15</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3297,7 +3064,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -3307,7 +3074,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2">
@@ -3317,27 +3084,27 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8">
@@ -3347,37 +3114,37 @@
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16">
@@ -3387,32 +3154,32 @@
     </row>
     <row r="17">
       <c r="A17" s="14" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23">
@@ -3422,17 +3189,17 @@
     </row>
     <row r="24">
       <c r="A24" s="14" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27">
@@ -3442,12 +3209,12 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
